--- a/test/moe_w8a8/channel-wsie_output.xlsx
+++ b/test/moe_w8a8/channel-wsie_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,25 +475,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C2" t="n">
         <v>7168</v>
       </c>
       <c r="D2" t="n">
-        <v>25.91999992728233</v>
+        <v>225.7599979639053</v>
       </c>
       <c r="E2" t="n">
         <v>7168</v>
       </c>
       <c r="F2" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G2" t="n">
-        <v>36.32000088691711</v>
+        <v>123.199000954628</v>
       </c>
       <c r="H2" t="n">
-        <v>109.219491481781</v>
+        <v>510.8256936073303</v>
       </c>
     </row>
     <row r="3">
@@ -501,25 +501,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C3" t="n">
         <v>7168</v>
       </c>
       <c r="D3" t="n">
-        <v>39.51999917626381</v>
+        <v>299.0390062332153</v>
       </c>
       <c r="E3" t="n">
         <v>7168</v>
       </c>
       <c r="F3" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G3" t="n">
-        <v>44.79999840259552</v>
+        <v>163.3599996566772</v>
       </c>
       <c r="H3" t="n">
-        <v>126.4088600873947</v>
+        <v>623.2961416244507</v>
       </c>
     </row>
     <row r="4">
@@ -527,25 +527,25 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C4" t="n">
         <v>7168</v>
       </c>
       <c r="D4" t="n">
-        <v>67.35999882221222</v>
+        <v>299.5994985103607</v>
       </c>
       <c r="E4" t="n">
         <v>7168</v>
       </c>
       <c r="F4" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G4" t="n">
-        <v>53.27999964356422</v>
+        <v>235.2000027894974</v>
       </c>
       <c r="H4" t="n">
-        <v>166.1825329065323</v>
+        <v>695.5711245536804</v>
       </c>
     </row>
     <row r="5">
@@ -553,25 +553,25 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C5" t="n">
         <v>7168</v>
       </c>
       <c r="D5" t="n">
-        <v>119.999997317791</v>
+        <v>360.6390058994293</v>
       </c>
       <c r="E5" t="n">
         <v>7168</v>
       </c>
       <c r="F5" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G5" t="n">
-        <v>72.31999933719635</v>
+        <v>254.8800110816956</v>
       </c>
       <c r="H5" t="n">
-        <v>246.0686713457108</v>
+        <v>782.210648059845</v>
       </c>
     </row>
     <row r="6">
@@ -579,25 +579,25 @@
         <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C6" t="n">
         <v>7168</v>
       </c>
       <c r="D6" t="n">
-        <v>189.9199932813644</v>
+        <v>353.7600040435791</v>
       </c>
       <c r="E6" t="n">
         <v>7168</v>
       </c>
       <c r="F6" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G6" t="n">
-        <v>97.9200005531311</v>
+        <v>267.1990096569061</v>
       </c>
       <c r="H6" t="n">
-        <v>344.4844186306</v>
+        <v>790.9703254699707</v>
       </c>
     </row>
     <row r="7">
@@ -605,25 +605,25 @@
         <v>32</v>
       </c>
       <c r="B7" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C7" t="n">
         <v>7168</v>
       </c>
       <c r="D7" t="n">
-        <v>313.2799863815308</v>
+        <v>362.0795011520386</v>
       </c>
       <c r="E7" t="n">
         <v>7168</v>
       </c>
       <c r="F7" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G7" t="n">
-        <v>146.7200070619583</v>
+        <v>374.2400109767914</v>
       </c>
       <c r="H7" t="n">
-        <v>516.7156457901001</v>
+        <v>914.0771627426147</v>
       </c>
     </row>
     <row r="8">
@@ -631,25 +631,25 @@
         <v>64</v>
       </c>
       <c r="B8" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C8" t="n">
         <v>7168</v>
       </c>
       <c r="D8" t="n">
-        <v>397.7600038051605</v>
+        <v>351.3599932193756</v>
       </c>
       <c r="E8" t="n">
         <v>7168</v>
       </c>
       <c r="F8" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G8" t="n">
-        <v>191.8399930000305</v>
+        <v>320.9599852561951</v>
       </c>
       <c r="H8" t="n">
-        <v>647.2985148429871</v>
+        <v>863.5736107826233</v>
       </c>
     </row>
     <row r="9">
@@ -657,25 +657,25 @@
         <v>128</v>
       </c>
       <c r="B9" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C9" t="n">
         <v>7168</v>
       </c>
       <c r="D9" t="n">
-        <v>450.8799910545349</v>
+        <v>355.3600013256073</v>
       </c>
       <c r="E9" t="n">
         <v>7168</v>
       </c>
       <c r="F9" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G9" t="n">
-        <v>225.7599979639053</v>
+        <v>395.359992980957</v>
       </c>
       <c r="H9" t="n">
-        <v>739.6135926246643</v>
+        <v>960.4361653327942</v>
       </c>
     </row>
     <row r="10">
@@ -683,25 +683,25 @@
         <v>256</v>
       </c>
       <c r="B10" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C10" t="n">
         <v>7168</v>
       </c>
       <c r="D10" t="n">
-        <v>592.7990078926086</v>
+        <v>454.3989896774292</v>
       </c>
       <c r="E10" t="n">
         <v>7168</v>
       </c>
       <c r="F10" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G10" t="n">
-        <v>311.5200102329254</v>
+        <v>758.2399845123291</v>
       </c>
       <c r="H10" t="n">
-        <v>994.1909313201904</v>
+        <v>1445.926427841187</v>
       </c>
     </row>
     <row r="11">
@@ -709,25 +709,25 @@
         <v>512</v>
       </c>
       <c r="B11" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C11" t="n">
         <v>7168</v>
       </c>
       <c r="D11" t="n">
-        <v>610.1599931716919</v>
+        <v>697.2789764404297</v>
       </c>
       <c r="E11" t="n">
         <v>7168</v>
       </c>
       <c r="F11" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G11" t="n">
-        <v>340.9599959850311</v>
+        <v>1145.918965339661</v>
       </c>
       <c r="H11" t="n">
-        <v>1056.173920631409</v>
+        <v>2154.80899810791</v>
       </c>
     </row>
     <row r="12">
@@ -735,25 +735,25 @@
         <v>1024</v>
       </c>
       <c r="B12" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C12" t="n">
         <v>7168</v>
       </c>
       <c r="D12" t="n">
-        <v>699.0394592285156</v>
+        <v>1163.679003715515</v>
       </c>
       <c r="E12" t="n">
         <v>7168</v>
       </c>
       <c r="F12" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G12" t="n">
-        <v>441.4399862289429</v>
+        <v>2065.91796875</v>
       </c>
       <c r="H12" t="n">
-        <v>1292.886734008789</v>
+        <v>3711.061000823975</v>
       </c>
     </row>
     <row r="13">
@@ -761,25 +761,25 @@
         <v>2048</v>
       </c>
       <c r="B13" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C13" t="n">
         <v>7168</v>
       </c>
       <c r="D13" t="n">
-        <v>933.9195489883423</v>
+        <v>2117.197513580322</v>
       </c>
       <c r="E13" t="n">
         <v>7168</v>
       </c>
       <c r="F13" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G13" t="n">
-        <v>661.9200110435486</v>
+        <v>4002.076148986816</v>
       </c>
       <c r="H13" t="n">
-        <v>1824.025392532349</v>
+        <v>6939.549446105957</v>
       </c>
     </row>
     <row r="14">
@@ -787,25 +787,25 @@
         <v>4096</v>
       </c>
       <c r="B14" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C14" t="n">
         <v>7168</v>
       </c>
       <c r="D14" t="n">
-        <v>1543.438911437988</v>
+        <v>4013.755798339844</v>
       </c>
       <c r="E14" t="n">
         <v>7168</v>
       </c>
       <c r="F14" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G14" t="n">
-        <v>1157.920002937317</v>
+        <v>7897.591590881348</v>
       </c>
       <c r="H14" t="n">
-        <v>3075.076103210449</v>
+        <v>13456.7403793335</v>
       </c>
     </row>
     <row r="15">
@@ -813,25 +813,25 @@
         <v>6144</v>
       </c>
       <c r="B15" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C15" t="n">
         <v>7168</v>
       </c>
       <c r="D15" t="n">
-        <v>1634.238958358765</v>
+        <v>5925.753593444824</v>
       </c>
       <c r="E15" t="n">
         <v>7168</v>
       </c>
       <c r="F15" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G15" t="n">
-        <v>2010.55908203125</v>
+        <v>11803.66802215576</v>
       </c>
       <c r="H15" t="n">
-        <v>4177.365303039551</v>
+        <v>19972.37968444824</v>
       </c>
     </row>
     <row r="16">
@@ -839,51 +839,25 @@
         <v>8192</v>
       </c>
       <c r="B16" t="n">
-        <v>256</v>
+        <v>4096</v>
       </c>
       <c r="C16" t="n">
         <v>7168</v>
       </c>
       <c r="D16" t="n">
-        <v>2008.479595184326</v>
+        <v>7744.152069091797</v>
       </c>
       <c r="E16" t="n">
         <v>7168</v>
       </c>
       <c r="F16" t="n">
-        <v>128</v>
+        <v>2048</v>
       </c>
       <c r="G16" t="n">
-        <v>2579.6799659729</v>
+        <v>15658.62369537354</v>
       </c>
       <c r="H16" t="n">
-        <v>5335.0830078125</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16384</v>
-      </c>
-      <c r="B17" t="n">
-        <v>256</v>
-      </c>
-      <c r="C17" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D17" t="n">
-        <v>5572.4778175354</v>
-      </c>
-      <c r="E17" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F17" t="n">
-        <v>128</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4291.838645935059</v>
-      </c>
-      <c r="H17" t="n">
-        <v>11210.43682098389</v>
+        <v>26289.78538513184</v>
       </c>
     </row>
   </sheetData>

--- a/test/moe_w8a8/channel-wsie_output.xlsx
+++ b/test/moe_w8a8/channel-wsie_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>1049</v>
       </c>
       <c r="B2" t="n">
         <v>4096</v>
@@ -481,7 +481,7 @@
         <v>7168</v>
       </c>
       <c r="D2" t="n">
-        <v>225.7599979639053</v>
+        <v>796.7990040779114</v>
       </c>
       <c r="E2" t="n">
         <v>7168</v>
@@ -490,374 +490,10 @@
         <v>2048</v>
       </c>
       <c r="G2" t="n">
-        <v>123.199000954628</v>
+        <v>580.7194709777832</v>
       </c>
       <c r="H2" t="n">
-        <v>510.8256936073303</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C3" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D3" t="n">
-        <v>299.0390062332153</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G3" t="n">
-        <v>163.3599996566772</v>
-      </c>
-      <c r="H3" t="n">
-        <v>623.2961416244507</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C4" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D4" t="n">
-        <v>299.5994985103607</v>
-      </c>
-      <c r="E4" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G4" t="n">
-        <v>235.2000027894974</v>
-      </c>
-      <c r="H4" t="n">
-        <v>695.5711245536804</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C5" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D5" t="n">
-        <v>360.6390058994293</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G5" t="n">
-        <v>254.8800110816956</v>
-      </c>
-      <c r="H5" t="n">
-        <v>782.210648059845</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C6" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D6" t="n">
-        <v>353.7600040435791</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G6" t="n">
-        <v>267.1990096569061</v>
-      </c>
-      <c r="H6" t="n">
-        <v>790.9703254699707</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D7" t="n">
-        <v>362.0795011520386</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G7" t="n">
-        <v>374.2400109767914</v>
-      </c>
-      <c r="H7" t="n">
-        <v>914.0771627426147</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>64</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D8" t="n">
-        <v>351.3599932193756</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G8" t="n">
-        <v>320.9599852561951</v>
-      </c>
-      <c r="H8" t="n">
-        <v>863.5736107826233</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>128</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C9" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D9" t="n">
-        <v>355.3600013256073</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G9" t="n">
-        <v>395.359992980957</v>
-      </c>
-      <c r="H9" t="n">
-        <v>960.4361653327942</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>256</v>
-      </c>
-      <c r="B10" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C10" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D10" t="n">
-        <v>454.3989896774292</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G10" t="n">
-        <v>758.2399845123291</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1445.926427841187</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>512</v>
-      </c>
-      <c r="B11" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C11" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D11" t="n">
-        <v>697.2789764404297</v>
-      </c>
-      <c r="E11" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1145.918965339661</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2154.80899810791</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1024</v>
-      </c>
-      <c r="B12" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C12" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1163.679003715515</v>
-      </c>
-      <c r="E12" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2065.91796875</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3711.061000823975</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2048</v>
-      </c>
-      <c r="B13" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C13" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2117.197513580322</v>
-      </c>
-      <c r="E13" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4002.076148986816</v>
-      </c>
-      <c r="H13" t="n">
-        <v>6939.549446105957</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>4096</v>
-      </c>
-      <c r="B14" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C14" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4013.755798339844</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G14" t="n">
-        <v>7897.591590881348</v>
-      </c>
-      <c r="H14" t="n">
-        <v>13456.7403793335</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>6144</v>
-      </c>
-      <c r="B15" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C15" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5925.753593444824</v>
-      </c>
-      <c r="E15" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G15" t="n">
-        <v>11803.66802215576</v>
-      </c>
-      <c r="H15" t="n">
-        <v>19972.37968444824</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>8192</v>
-      </c>
-      <c r="B16" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C16" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D16" t="n">
-        <v>7744.152069091797</v>
-      </c>
-      <c r="E16" t="n">
-        <v>7168</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2048</v>
-      </c>
-      <c r="G16" t="n">
-        <v>15658.62369537354</v>
-      </c>
-      <c r="H16" t="n">
-        <v>26289.78538513184</v>
+        <v>5929.843902587891</v>
       </c>
     </row>
   </sheetData>

--- a/test/moe_w8a8/channel-wsie_output.xlsx
+++ b/test/moe_w8a8/channel-wsie_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,28 +472,210 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1049</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4096</v>
+        <v>256</v>
       </c>
       <c r="C2" t="n">
         <v>7168</v>
       </c>
       <c r="D2" t="n">
-        <v>796.7990040779114</v>
+        <v>25.5999993532896</v>
       </c>
       <c r="E2" t="n">
         <v>7168</v>
       </c>
       <c r="F2" t="n">
-        <v>2048</v>
+        <v>128</v>
       </c>
       <c r="G2" t="n">
-        <v>580.7194709777832</v>
+        <v>38.2389985024929</v>
       </c>
       <c r="H2" t="n">
-        <v>5929.843902587891</v>
+        <v>162.4616831541061</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>256</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D3" t="n">
+        <v>39.20000046491623</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7168</v>
+      </c>
+      <c r="F3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G3" t="n">
+        <v>45.43999955058098</v>
+      </c>
+      <c r="H3" t="n">
+        <v>131.0573369264603</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
+        <v>256</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D4" t="n">
+        <v>59.03999879956245</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7168</v>
+      </c>
+      <c r="F4" t="n">
+        <v>128</v>
+      </c>
+      <c r="G4" t="n">
+        <v>53.11999842524529</v>
+      </c>
+      <c r="H4" t="n">
+        <v>159.8783135414124</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>256</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D5" t="n">
+        <v>110.7200011610985</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7168</v>
+      </c>
+      <c r="F5" t="n">
+        <v>128</v>
+      </c>
+      <c r="G5" t="n">
+        <v>72.80000299215317</v>
+      </c>
+      <c r="H5" t="n">
+        <v>236.8245124816895</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>256</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D6" t="n">
+        <v>188.3189976215363</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7168</v>
+      </c>
+      <c r="F6" t="n">
+        <v>128</v>
+      </c>
+      <c r="G6" t="n">
+        <v>106.0800030827522</v>
+      </c>
+      <c r="H6" t="n">
+        <v>350.0251173973083</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B7" t="n">
+        <v>256</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D7" t="n">
+        <v>269.118994474411</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7168</v>
+      </c>
+      <c r="F7" t="n">
+        <v>128</v>
+      </c>
+      <c r="G7" t="n">
+        <v>142.3989981412888</v>
+      </c>
+      <c r="H7" t="n">
+        <v>466.7013585567474</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B8" t="n">
+        <v>256</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D8" t="n">
+        <v>379.5995116233826</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7168</v>
+      </c>
+      <c r="F8" t="n">
+        <v>128</v>
+      </c>
+      <c r="G8" t="n">
+        <v>193.2799965143204</v>
+      </c>
+      <c r="H8" t="n">
+        <v>630.9561729431152</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128</v>
+      </c>
+      <c r="B9" t="n">
+        <v>256</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D9" t="n">
+        <v>427.359014749527</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7168</v>
+      </c>
+      <c r="F9" t="n">
+        <v>128</v>
+      </c>
+      <c r="G9" t="n">
+        <v>228.7999987602234</v>
+      </c>
+      <c r="H9" t="n">
+        <v>714.0725255012512</v>
       </c>
     </row>
   </sheetData>

--- a/test/moe_w8a8/channel-wsie_output.xlsx
+++ b/test/moe_w8a8/channel-wsie_output.xlsx
@@ -481,7 +481,7 @@
         <v>7168</v>
       </c>
       <c r="D2" t="n">
-        <v>25.5999993532896</v>
+        <v>24.32000078260899</v>
       </c>
       <c r="E2" t="n">
         <v>7168</v>
@@ -490,10 +490,10 @@
         <v>128</v>
       </c>
       <c r="G2" t="n">
-        <v>38.2389985024929</v>
+        <v>38.24000060558319</v>
       </c>
       <c r="H2" t="n">
-        <v>162.4616831541061</v>
+        <v>142.632395029068</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         <v>7168</v>
       </c>
       <c r="D3" t="n">
-        <v>39.20000046491623</v>
+        <v>39.51999917626381</v>
       </c>
       <c r="E3" t="n">
         <v>7168</v>
@@ -519,7 +519,7 @@
         <v>45.43999955058098</v>
       </c>
       <c r="H3" t="n">
-        <v>131.0573369264603</v>
+        <v>140.5530422925949</v>
       </c>
     </row>
     <row r="4">
@@ -533,7 +533,7 @@
         <v>7168</v>
       </c>
       <c r="D4" t="n">
-        <v>59.03999879956245</v>
+        <v>66.56000018119812</v>
       </c>
       <c r="E4" t="n">
         <v>7168</v>
@@ -542,10 +542,10 @@
         <v>128</v>
       </c>
       <c r="G4" t="n">
-        <v>53.11999842524529</v>
+        <v>54.23999950289726</v>
       </c>
       <c r="H4" t="n">
-        <v>159.8783135414124</v>
+        <v>168.8819378614426</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>7168</v>
       </c>
       <c r="D5" t="n">
-        <v>110.7200011610985</v>
+        <v>107.3599979281425</v>
       </c>
       <c r="E5" t="n">
         <v>7168</v>
@@ -568,10 +568,10 @@
         <v>128</v>
       </c>
       <c r="G5" t="n">
-        <v>72.80000299215317</v>
+        <v>70.88000327348709</v>
       </c>
       <c r="H5" t="n">
-        <v>236.8245124816895</v>
+        <v>232.1523725986481</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         <v>7168</v>
       </c>
       <c r="D6" t="n">
-        <v>188.3189976215363</v>
+        <v>187.5189989805222</v>
       </c>
       <c r="E6" t="n">
         <v>7168</v>
@@ -594,10 +594,10 @@
         <v>128</v>
       </c>
       <c r="G6" t="n">
-        <v>106.0800030827522</v>
+        <v>105.4399982094765</v>
       </c>
       <c r="H6" t="n">
-        <v>350.0251173973083</v>
+        <v>349.6241569519043</v>
       </c>
     </row>
     <row r="7">
@@ -611,7 +611,7 @@
         <v>7168</v>
       </c>
       <c r="D7" t="n">
-        <v>269.118994474411</v>
+        <v>290.0789976119995</v>
       </c>
       <c r="E7" t="n">
         <v>7168</v>
@@ -620,10 +620,10 @@
         <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>142.3989981412888</v>
+        <v>150.7200002670288</v>
       </c>
       <c r="H7" t="n">
-        <v>466.7013585567474</v>
+        <v>498.2242584228516</v>
       </c>
     </row>
     <row r="8">
@@ -637,7 +637,7 @@
         <v>7168</v>
       </c>
       <c r="D8" t="n">
-        <v>379.5995116233826</v>
+        <v>468.799501657486</v>
       </c>
       <c r="E8" t="n">
         <v>7168</v>
@@ -646,10 +646,10 @@
         <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>193.2799965143204</v>
+        <v>212.4799937009811</v>
       </c>
       <c r="H8" t="n">
-        <v>630.9561729431152</v>
+        <v>741.7557239532471</v>
       </c>
     </row>
     <row r="9">
@@ -663,7 +663,7 @@
         <v>7168</v>
       </c>
       <c r="D9" t="n">
-        <v>427.359014749527</v>
+        <v>560.6390237808228</v>
       </c>
       <c r="E9" t="n">
         <v>7168</v>
@@ -672,10 +672,10 @@
         <v>128</v>
       </c>
       <c r="G9" t="n">
-        <v>228.7999987602234</v>
+        <v>246.8799948692322</v>
       </c>
       <c r="H9" t="n">
-        <v>714.0725255012512</v>
+        <v>872.346818447113</v>
       </c>
     </row>
   </sheetData>

--- a/test/moe_w8a8/channel-wsie_output.xlsx
+++ b/test/moe_w8a8/channel-wsie_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,25 +475,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>256</v>
+        <v>1536</v>
       </c>
       <c r="C2" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="D2" t="n">
-        <v>24.32000078260899</v>
+        <v>31.36000037193298</v>
       </c>
       <c r="E2" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="F2" t="n">
-        <v>128</v>
+        <v>768</v>
       </c>
       <c r="G2" t="n">
-        <v>38.24000060558319</v>
+        <v>22.08000048995018</v>
       </c>
       <c r="H2" t="n">
-        <v>142.632395029068</v>
+        <v>153.3833146095276</v>
       </c>
     </row>
     <row r="3">
@@ -501,25 +501,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>256</v>
+        <v>1536</v>
       </c>
       <c r="C3" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="D3" t="n">
-        <v>39.51999917626381</v>
+        <v>52.79900133609772</v>
       </c>
       <c r="E3" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="F3" t="n">
-        <v>128</v>
+        <v>768</v>
       </c>
       <c r="G3" t="n">
-        <v>45.43999955058098</v>
+        <v>31.67999908328056</v>
       </c>
       <c r="H3" t="n">
-        <v>140.5530422925949</v>
+        <v>137.3339742422104</v>
       </c>
     </row>
     <row r="4">
@@ -527,25 +527,25 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>256</v>
+        <v>1536</v>
       </c>
       <c r="C4" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="D4" t="n">
-        <v>66.56000018119812</v>
+        <v>90.87999910116196</v>
       </c>
       <c r="E4" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="F4" t="n">
-        <v>128</v>
+        <v>768</v>
       </c>
       <c r="G4" t="n">
-        <v>54.23999950289726</v>
+        <v>52.31999978423119</v>
       </c>
       <c r="H4" t="n">
-        <v>168.8819378614426</v>
+        <v>183.2870244979858</v>
       </c>
     </row>
     <row r="5">
@@ -553,25 +553,25 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>256</v>
+        <v>1536</v>
       </c>
       <c r="C5" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="D5" t="n">
-        <v>107.3599979281425</v>
+        <v>141.1200016736984</v>
       </c>
       <c r="E5" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="F5" t="n">
-        <v>128</v>
+        <v>768</v>
       </c>
       <c r="G5" t="n">
-        <v>70.88000327348709</v>
+        <v>78.5600021481514</v>
       </c>
       <c r="H5" t="n">
-        <v>232.1523725986481</v>
+        <v>265.7933533191681</v>
       </c>
     </row>
     <row r="6">
@@ -579,25 +579,25 @@
         <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>256</v>
+        <v>1536</v>
       </c>
       <c r="C6" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="D6" t="n">
-        <v>187.5189989805222</v>
+        <v>227.3599952459335</v>
       </c>
       <c r="E6" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="F6" t="n">
-        <v>128</v>
+        <v>768</v>
       </c>
       <c r="G6" t="n">
-        <v>105.4399982094765</v>
+        <v>123.8399967551231</v>
       </c>
       <c r="H6" t="n">
-        <v>349.6241569519043</v>
+        <v>399.8547196388245</v>
       </c>
     </row>
     <row r="7">
@@ -605,25 +605,25 @@
         <v>32</v>
       </c>
       <c r="B7" t="n">
-        <v>256</v>
+        <v>1536</v>
       </c>
       <c r="C7" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="D7" t="n">
-        <v>290.0789976119995</v>
+        <v>307.9990148544312</v>
       </c>
       <c r="E7" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="F7" t="n">
-        <v>128</v>
+        <v>768</v>
       </c>
       <c r="G7" t="n">
-        <v>150.7200002670288</v>
+        <v>159.5200002193451</v>
       </c>
       <c r="H7" t="n">
-        <v>498.2242584228516</v>
+        <v>528.9741158485413</v>
       </c>
     </row>
     <row r="8">
@@ -631,25 +631,25 @@
         <v>64</v>
       </c>
       <c r="B8" t="n">
-        <v>256</v>
+        <v>1536</v>
       </c>
       <c r="C8" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="D8" t="n">
-        <v>468.799501657486</v>
+        <v>353.5999953746796</v>
       </c>
       <c r="E8" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="F8" t="n">
-        <v>128</v>
+        <v>768</v>
       </c>
       <c r="G8" t="n">
-        <v>212.4799937009811</v>
+        <v>183.0399930477142</v>
       </c>
       <c r="H8" t="n">
-        <v>741.7557239532471</v>
+        <v>589.924693107605</v>
       </c>
     </row>
     <row r="9">
@@ -657,25 +657,441 @@
         <v>128</v>
       </c>
       <c r="B9" t="n">
-        <v>256</v>
+        <v>1536</v>
       </c>
       <c r="C9" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="D9" t="n">
-        <v>560.6390237808228</v>
+        <v>377.5995075702667</v>
       </c>
       <c r="E9" t="n">
-        <v>7168</v>
+        <v>2048</v>
       </c>
       <c r="F9" t="n">
+        <v>768</v>
+      </c>
+      <c r="G9" t="n">
+        <v>199.520006775856</v>
+      </c>
+      <c r="H9" t="n">
+        <v>640.6465172767639</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>768</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D10" t="n">
+        <v>23.36000092327595</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F10" t="n">
+        <v>384</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16.64000004529953</v>
+      </c>
+      <c r="H10" t="n">
+        <v>141.3276046514511</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="n">
+        <v>768</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D11" t="n">
+        <v>31.52000159025192</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F11" t="n">
+        <v>384</v>
+      </c>
+      <c r="G11" t="n">
+        <v>21.91999927163124</v>
+      </c>
+      <c r="H11" t="n">
+        <v>141.374409198761</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" t="n">
+        <v>768</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D12" t="n">
+        <v>49.60000142455101</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F12" t="n">
+        <v>384</v>
+      </c>
+      <c r="G12" t="n">
+        <v>28.96000072360039</v>
+      </c>
+      <c r="H12" t="n">
+        <v>140.1913613080978</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="n">
+        <v>768</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D13" t="n">
+        <v>78.5600021481514</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F13" t="n">
+        <v>384</v>
+      </c>
+      <c r="G13" t="n">
+        <v>43.99999976158142</v>
+      </c>
+      <c r="H13" t="n">
+        <v>168.8511371612549</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" t="n">
+        <v>768</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D14" t="n">
+        <v>116.6395023465157</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F14" t="n">
+        <v>384</v>
+      </c>
+      <c r="G14" t="n">
+        <v>64.00000303983688</v>
+      </c>
+      <c r="H14" t="n">
+        <v>228.1064838171005</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>32</v>
+      </c>
+      <c r="B15" t="n">
+        <v>768</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D15" t="n">
+        <v>155.5200070142746</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F15" t="n">
+        <v>384</v>
+      </c>
+      <c r="G15" t="n">
+        <v>83.83999764919281</v>
+      </c>
+      <c r="H15" t="n">
+        <v>288.6161506175995</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>64</v>
+      </c>
+      <c r="B16" t="n">
+        <v>768</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D16" t="n">
+        <v>180.9599995613098</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F16" t="n">
+        <v>384</v>
+      </c>
+      <c r="G16" t="n">
+        <v>97.43999689817429</v>
+      </c>
+      <c r="H16" t="n">
+        <v>345.560222864151</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>128</v>
       </c>
-      <c r="G9" t="n">
-        <v>246.8799948692322</v>
-      </c>
-      <c r="H9" t="n">
-        <v>872.346818447113</v>
+      <c r="B17" t="n">
+        <v>768</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D17" t="n">
+        <v>193.9200013875961</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F17" t="n">
+        <v>384</v>
+      </c>
+      <c r="G17" t="n">
+        <v>105.7600006461143</v>
+      </c>
+      <c r="H17" t="n">
+        <v>358.7374091148376</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>384</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D18" t="n">
+        <v>23.84000085294247</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F18" t="n">
+        <v>192</v>
+      </c>
+      <c r="G18" t="n">
+        <v>17.27999933063984</v>
+      </c>
+      <c r="H18" t="n">
+        <v>143.3312147855759</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="n">
+        <v>384</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D19" t="n">
+        <v>32.00000151991844</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F19" t="n">
+        <v>192</v>
+      </c>
+      <c r="G19" t="n">
+        <v>22.23999984562397</v>
+      </c>
+      <c r="H19" t="n">
+        <v>141.7538672685623</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" t="n">
+        <v>384</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D20" t="n">
+        <v>50.23999884724617</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F20" t="n">
+        <v>192</v>
+      </c>
+      <c r="G20" t="n">
+        <v>31.8400003015995</v>
+      </c>
+      <c r="H20" t="n">
+        <v>142.4433141946793</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" t="n">
+        <v>384</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D21" t="n">
+        <v>79.99999821186066</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F21" t="n">
+        <v>192</v>
+      </c>
+      <c r="G21" t="n">
+        <v>47.68000170588493</v>
+      </c>
+      <c r="H21" t="n">
+        <v>174.5042353868484</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" t="n">
+        <v>384</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D22" t="n">
+        <v>126.7199963331223</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F22" t="n">
+        <v>192</v>
+      </c>
+      <c r="G22" t="n">
+        <v>70.88000327348709</v>
+      </c>
+      <c r="H22" t="n">
+        <v>244.5713877677917</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>32</v>
+      </c>
+      <c r="B23" t="n">
+        <v>384</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D23" t="n">
+        <v>160.6400012969971</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F23" t="n">
+        <v>192</v>
+      </c>
+      <c r="G23" t="n">
+        <v>90.2400016784668</v>
+      </c>
+      <c r="H23" t="n">
+        <v>301.0494112968445</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>64</v>
+      </c>
+      <c r="B24" t="n">
+        <v>384</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D24" t="n">
+        <v>178.399994969368</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F24" t="n">
+        <v>192</v>
+      </c>
+      <c r="G24" t="n">
+        <v>104.4799983501434</v>
+      </c>
+      <c r="H24" t="n">
+        <v>336.4949524402618</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128</v>
+      </c>
+      <c r="B25" t="n">
+        <v>384</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D25" t="n">
+        <v>189.1189962625504</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F25" t="n">
+        <v>192</v>
+      </c>
+      <c r="G25" t="n">
+        <v>114.7190034389496</v>
+      </c>
+      <c r="H25" t="n">
+        <v>381.9837272167206</v>
       </c>
     </row>
   </sheetData>
